--- a/artfynd/A 23421-2026 artfynd.xlsx
+++ b/artfynd/A 23421-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232481</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134232482</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>134232483</v>
       </c>
       <c r="B4" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>134232480</v>
       </c>
       <c r="B5" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>134232484</v>
       </c>
       <c r="B6" t="n">
-        <v>97291</v>
+        <v>97293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23421-2026 artfynd.xlsx
+++ b/artfynd/A 23421-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232481</v>
       </c>
       <c r="B2" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134232482</v>
       </c>
       <c r="B3" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>134232483</v>
       </c>
       <c r="B4" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>134232480</v>
       </c>
       <c r="B5" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>134232484</v>
       </c>
       <c r="B6" t="n">
-        <v>97294</v>
+        <v>97301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23421-2026 artfynd.xlsx
+++ b/artfynd/A 23421-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134232481</v>
+        <v>134232484</v>
       </c>
       <c r="B2" t="n">
-        <v>98056</v>
+        <v>97308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483010</v>
+        <v>483088</v>
       </c>
       <c r="R2" t="n">
-        <v>6594486</v>
+        <v>6594422</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232482</v>
+        <v>134232480</v>
       </c>
       <c r="B3" t="n">
-        <v>98056</v>
+        <v>98063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483203</v>
+        <v>482995</v>
       </c>
       <c r="R3" t="n">
-        <v>6594516</v>
+        <v>6594468</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232483</v>
+        <v>134232481</v>
       </c>
       <c r="B4" t="n">
-        <v>98056</v>
+        <v>98063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483115</v>
+        <v>483010</v>
       </c>
       <c r="R4" t="n">
-        <v>6594434</v>
+        <v>6594486</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134232480</v>
+        <v>134232482</v>
       </c>
       <c r="B5" t="n">
-        <v>98056</v>
+        <v>98063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482995</v>
+        <v>483203</v>
       </c>
       <c r="R5" t="n">
-        <v>6594468</v>
+        <v>6594516</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134232484</v>
+        <v>134232483</v>
       </c>
       <c r="B6" t="n">
-        <v>97301</v>
+        <v>98063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483088</v>
+        <v>483115</v>
       </c>
       <c r="R6" t="n">
-        <v>6594422</v>
+        <v>6594434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23421-2026 artfynd.xlsx
+++ b/artfynd/A 23421-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232480</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232483</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>